--- a/data/nzd0481/nzd0481.xlsx
+++ b/data/nzd0481/nzd0481.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K665"/>
+  <dimension ref="A1:K667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26375,6 +26375,84 @@
       <c r="K665" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>328.77</v>
+      </c>
+      <c r="C666" t="n">
+        <v>339.62</v>
+      </c>
+      <c r="D666" t="n">
+        <v>347.32</v>
+      </c>
+      <c r="E666" t="n">
+        <v>341.71</v>
+      </c>
+      <c r="F666" t="n">
+        <v>344.89</v>
+      </c>
+      <c r="G666" t="n">
+        <v>352.32</v>
+      </c>
+      <c r="H666" t="n">
+        <v>356.11</v>
+      </c>
+      <c r="I666" t="n">
+        <v>360.25</v>
+      </c>
+      <c r="J666" t="n">
+        <v>369.17</v>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>329.91</v>
+      </c>
+      <c r="C667" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="D667" t="n">
+        <v>347.89</v>
+      </c>
+      <c r="E667" t="n">
+        <v>342.19</v>
+      </c>
+      <c r="F667" t="n">
+        <v>345.17</v>
+      </c>
+      <c r="G667" t="n">
+        <v>351.81</v>
+      </c>
+      <c r="H667" t="n">
+        <v>356.01</v>
+      </c>
+      <c r="I667" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="J667" t="n">
+        <v>369.68</v>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -26389,7 +26467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B723"/>
+  <dimension ref="A1:B725"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33622,6 +33700,26 @@
       </c>
       <c r="B723" t="n">
         <v>0.67</v>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B724" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B725" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -33790,28 +33888,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07886334100924453</v>
+        <v>-0.08100062035438867</v>
       </c>
       <c r="J2" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K2" t="n">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003699732999971506</v>
+        <v>0.003924635885450223</v>
       </c>
       <c r="M2" t="n">
-        <v>7.439861931526188</v>
+        <v>7.427250230800387</v>
       </c>
       <c r="N2" t="n">
-        <v>74.89164099502861</v>
+        <v>74.70029091704095</v>
       </c>
       <c r="O2" t="n">
-        <v>8.653995666455387</v>
+        <v>8.642933004312885</v>
       </c>
       <c r="P2" t="n">
-        <v>334.7367734161021</v>
+        <v>334.7624687776513</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33872,28 +33970,28 @@
         <v>0.073</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.164777502819164</v>
+        <v>-0.168334720535515</v>
       </c>
       <c r="J3" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K3" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09516418959765205</v>
+        <v>0.09874881472173702</v>
       </c>
       <c r="M3" t="n">
-        <v>2.790175509997915</v>
+        <v>2.799343504875762</v>
       </c>
       <c r="N3" t="n">
-        <v>11.63445302158767</v>
+        <v>11.69219011425076</v>
       </c>
       <c r="O3" t="n">
-        <v>3.410931400891502</v>
+        <v>3.419384464234866</v>
       </c>
       <c r="P3" t="n">
-        <v>349.9110332476449</v>
+        <v>349.9536261795931</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -33954,28 +34052,28 @@
         <v>0.0871</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06263130032100525</v>
+        <v>-0.06490792854802346</v>
       </c>
       <c r="J4" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K4" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02005251843946088</v>
+        <v>0.02154243781777754</v>
       </c>
       <c r="M4" t="n">
-        <v>2.382557735895211</v>
+        <v>2.385188995747636</v>
       </c>
       <c r="N4" t="n">
-        <v>8.639142616524536</v>
+        <v>8.651215916079529</v>
       </c>
       <c r="O4" t="n">
-        <v>2.939241843830571</v>
+        <v>2.941294938641742</v>
       </c>
       <c r="P4" t="n">
-        <v>352.8132082928743</v>
+        <v>352.8404677588509</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34032,28 +34130,28 @@
         <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1234677168407082</v>
+        <v>-0.1251350098442381</v>
       </c>
       <c r="J5" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K5" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07057726614748216</v>
+        <v>0.07262123361082318</v>
       </c>
       <c r="M5" t="n">
-        <v>2.288777795865287</v>
+        <v>2.289246851776997</v>
       </c>
       <c r="N5" t="n">
-        <v>9.047096109199771</v>
+        <v>9.040359405720782</v>
       </c>
       <c r="O5" t="n">
-        <v>3.007839109593426</v>
+        <v>3.006719043362845</v>
       </c>
       <c r="P5" t="n">
-        <v>347.8041370934762</v>
+        <v>347.8241005110918</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34110,28 +34208,28 @@
         <v>0.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1693905581895029</v>
+        <v>-0.1700254140944902</v>
       </c>
       <c r="J6" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K6" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1565792718526297</v>
+        <v>0.1583352957339094</v>
       </c>
       <c r="M6" t="n">
-        <v>2.016529184854936</v>
+        <v>2.013331366441343</v>
       </c>
       <c r="N6" t="n">
-        <v>6.965339818589271</v>
+        <v>6.947420189278875</v>
       </c>
       <c r="O6" t="n">
-        <v>2.63919302412485</v>
+        <v>2.635795930886698</v>
       </c>
       <c r="P6" t="n">
-        <v>350.4740781360221</v>
+        <v>350.4816794465192</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34188,28 +34286,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1884719740537964</v>
+        <v>-0.1899649378062639</v>
       </c>
       <c r="J7" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K7" t="n">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1403329397806377</v>
+        <v>0.1427997351708843</v>
       </c>
       <c r="M7" t="n">
-        <v>2.462119726440173</v>
+        <v>2.461637324116954</v>
       </c>
       <c r="N7" t="n">
-        <v>9.768331814516477</v>
+        <v>9.755296096158194</v>
       </c>
       <c r="O7" t="n">
-        <v>3.125433060316039</v>
+        <v>3.123346938167163</v>
       </c>
       <c r="P7" t="n">
-        <v>359.3479387546724</v>
+        <v>359.3658584366428</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34266,28 +34364,28 @@
         <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1827601987005049</v>
+        <v>-0.1841096254334934</v>
       </c>
       <c r="J8" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K8" t="n">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1601740886076799</v>
+        <v>0.1627771745498813</v>
       </c>
       <c r="M8" t="n">
-        <v>2.125213747467552</v>
+        <v>2.12584619430542</v>
       </c>
       <c r="N8" t="n">
-        <v>7.861699382767185</v>
+        <v>7.851257203741371</v>
       </c>
       <c r="O8" t="n">
-        <v>2.803872212274872</v>
+        <v>2.802009493870671</v>
       </c>
       <c r="P8" t="n">
-        <v>362.9680663210937</v>
+        <v>362.9842625417386</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34344,28 +34442,28 @@
         <v>0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07122473396957843</v>
+        <v>-0.07201526565147759</v>
       </c>
       <c r="J9" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K9" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02260001485592344</v>
+        <v>0.02322222304246335</v>
       </c>
       <c r="M9" t="n">
-        <v>2.393328450171487</v>
+        <v>2.390233741195072</v>
       </c>
       <c r="N9" t="n">
-        <v>9.887333540554822</v>
+        <v>9.862241174073457</v>
       </c>
       <c r="O9" t="n">
-        <v>3.144413067736938</v>
+        <v>3.140420540958401</v>
       </c>
       <c r="P9" t="n">
-        <v>363.4868809218838</v>
+        <v>363.4963463644353</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34422,28 +34520,28 @@
         <v>0.097</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09031469769979218</v>
+        <v>-0.09134148842343107</v>
       </c>
       <c r="J10" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="K10" t="n">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="L10" t="n">
-        <v>0.03961128178146534</v>
+        <v>0.04068678412390325</v>
       </c>
       <c r="M10" t="n">
-        <v>2.279974445867014</v>
+        <v>2.277928703878335</v>
       </c>
       <c r="N10" t="n">
-        <v>8.912487399567262</v>
+        <v>8.89360296907663</v>
       </c>
       <c r="O10" t="n">
-        <v>2.985378937349036</v>
+        <v>2.9822144404916</v>
       </c>
       <c r="P10" t="n">
-        <v>373.408081120679</v>
+        <v>373.4203750867156</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34481,7 +34579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K665"/>
+  <dimension ref="A1:K667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72377,6 +72475,120 @@
         </is>
       </c>
     </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:32+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>-45.260310798252014,170.86118449474955</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>-45.26084796002144,170.86069305342073</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>-45.26127399052782,170.86004064263898</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>-45.26174208070191,170.85946681153965</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>-45.262316297086905,170.85910128258388</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>-45.262935313853944,170.85892000796218</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>-45.26353909903707,170.85872271371443</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>-45.26414131874531,170.85869651376862</t>
+        </is>
+      </c>
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>-45.26474597131393,170.85889023892207</t>
+        </is>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-15 22:14:52+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-45.260317732174194,170.8611951991109</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-45.26085328378425,170.8606997237634</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-45.26127767394387,170.8600456967024</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>-45.26174440328772,170.85947196802545</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>-45.26231729346318,170.85910455945378</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>-45.26293389869914,170.85891382627582</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>-45.26353891470934,170.85872146653105</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>-45.26414136564692,170.8586996986191</t>
+        </is>
+      </c>
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>-45.26474564420265,170.85889672096934</t>
+        </is>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0481/nzd0481.xlsx
+++ b/data/nzd0481/nzd0481.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K667"/>
+  <dimension ref="A1:K669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26453,6 +26453,84 @@
       <c r="K667" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>330.3</v>
+      </c>
+      <c r="C668" t="n">
+        <v>340.49</v>
+      </c>
+      <c r="D668" t="n">
+        <v>347.54</v>
+      </c>
+      <c r="E668" t="n">
+        <v>341.57</v>
+      </c>
+      <c r="F668" t="n">
+        <v>344.65</v>
+      </c>
+      <c r="G668" t="n">
+        <v>351.24</v>
+      </c>
+      <c r="H668" t="n">
+        <v>355.66</v>
+      </c>
+      <c r="I668" t="n">
+        <v>360.24</v>
+      </c>
+      <c r="J668" t="n">
+        <v>369.63</v>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>331.93</v>
+      </c>
+      <c r="C669" t="n">
+        <v>340.24</v>
+      </c>
+      <c r="D669" t="n">
+        <v>347.16</v>
+      </c>
+      <c r="E669" t="n">
+        <v>340.82</v>
+      </c>
+      <c r="F669" t="n">
+        <v>343.82</v>
+      </c>
+      <c r="G669" t="n">
+        <v>350.41</v>
+      </c>
+      <c r="H669" t="n">
+        <v>354.78</v>
+      </c>
+      <c r="I669" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="J669" t="n">
+        <v>369.24</v>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26467,7 +26545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B725"/>
+  <dimension ref="A1:B727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33720,6 +33798,26 @@
       </c>
       <c r="B725" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B726" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B727" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -33888,28 +33986,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08100062035438867</v>
+        <v>-0.08196957488010517</v>
       </c>
       <c r="J2" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K2" t="n">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003924635885450223</v>
+        <v>0.004043084223136373</v>
       </c>
       <c r="M2" t="n">
-        <v>7.427250230800387</v>
+        <v>7.4093745514876</v>
       </c>
       <c r="N2" t="n">
-        <v>74.70029091704095</v>
+        <v>74.48512860553161</v>
       </c>
       <c r="O2" t="n">
-        <v>8.642933004312885</v>
+        <v>8.630476731069473</v>
       </c>
       <c r="P2" t="n">
-        <v>334.7624687776513</v>
+        <v>334.7741353917766</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -33970,28 +34068,28 @@
         <v>0.073</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.168334720535515</v>
+        <v>-0.1716124706758435</v>
       </c>
       <c r="J3" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K3" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09874881472173702</v>
+        <v>0.1021818873325893</v>
       </c>
       <c r="M3" t="n">
-        <v>2.799343504875762</v>
+        <v>2.807054315148046</v>
       </c>
       <c r="N3" t="n">
-        <v>11.69219011425076</v>
+        <v>11.73603314144617</v>
       </c>
       <c r="O3" t="n">
-        <v>3.419384464234866</v>
+        <v>3.425789418724707</v>
       </c>
       <c r="P3" t="n">
-        <v>349.9536261795931</v>
+        <v>349.9929399941998</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34052,28 +34150,28 @@
         <v>0.0871</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06490792854802346</v>
+        <v>-0.06731190291529399</v>
       </c>
       <c r="J4" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K4" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02154243781777754</v>
+        <v>0.02315835169218272</v>
       </c>
       <c r="M4" t="n">
-        <v>2.385188995747636</v>
+        <v>2.388398089963014</v>
       </c>
       <c r="N4" t="n">
-        <v>8.651215916079529</v>
+        <v>8.667811463311553</v>
       </c>
       <c r="O4" t="n">
-        <v>2.941294938641742</v>
+        <v>2.944114716398047</v>
       </c>
       <c r="P4" t="n">
-        <v>352.8404677588509</v>
+        <v>352.8693017249809</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34130,28 +34228,28 @@
         <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1251350098442381</v>
+        <v>-0.1272526992709782</v>
       </c>
       <c r="J5" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K5" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07262123361082318</v>
+        <v>0.0750860581173064</v>
       </c>
       <c r="M5" t="n">
-        <v>2.289246851776997</v>
+        <v>2.291707319639645</v>
       </c>
       <c r="N5" t="n">
-        <v>9.040359405720782</v>
+        <v>9.046596584727142</v>
       </c>
       <c r="O5" t="n">
-        <v>3.006719043362845</v>
+        <v>3.007756071347399</v>
       </c>
       <c r="P5" t="n">
-        <v>347.8241005110918</v>
+        <v>347.8495013851625</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34208,28 +34306,28 @@
         <v>0.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1700254140944902</v>
+        <v>-0.1711516671633847</v>
       </c>
       <c r="J6" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K6" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1583352957339094</v>
+        <v>0.1607423552901694</v>
       </c>
       <c r="M6" t="n">
-        <v>2.013331366441343</v>
+        <v>2.012333496273082</v>
       </c>
       <c r="N6" t="n">
-        <v>6.947420189278875</v>
+        <v>6.936436949889417</v>
       </c>
       <c r="O6" t="n">
-        <v>2.635795930886698</v>
+        <v>2.633711629979527</v>
       </c>
       <c r="P6" t="n">
-        <v>350.4816794465192</v>
+        <v>350.4951891614884</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34286,28 +34384,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1899649378062639</v>
+        <v>-0.1922245426062458</v>
       </c>
       <c r="J7" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K7" t="n">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1427997351708843</v>
+        <v>0.1460055049711214</v>
       </c>
       <c r="M7" t="n">
-        <v>2.461637324116954</v>
+        <v>2.464654951342004</v>
       </c>
       <c r="N7" t="n">
-        <v>9.755296096158194</v>
+        <v>9.763797059530846</v>
       </c>
       <c r="O7" t="n">
-        <v>3.123346938167163</v>
+        <v>3.124707515837418</v>
       </c>
       <c r="P7" t="n">
-        <v>359.3658584366428</v>
+        <v>359.3930251422227</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34364,28 +34462,28 @@
         <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1841096254334934</v>
+        <v>-0.185971414677683</v>
       </c>
       <c r="J8" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K8" t="n">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1627771745498813</v>
+        <v>0.1659356758314552</v>
       </c>
       <c r="M8" t="n">
-        <v>2.12584619430542</v>
+        <v>2.129113622760431</v>
       </c>
       <c r="N8" t="n">
-        <v>7.851257203741371</v>
+        <v>7.853575035354067</v>
       </c>
       <c r="O8" t="n">
-        <v>2.802009493870671</v>
+        <v>2.802423065019639</v>
       </c>
       <c r="P8" t="n">
-        <v>362.9842625417386</v>
+        <v>363.0066467430654</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34442,28 +34540,28 @@
         <v>0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07201526565147759</v>
+        <v>-0.07311423093058911</v>
       </c>
       <c r="J9" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K9" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02322222304246335</v>
+        <v>0.02404154069607967</v>
       </c>
       <c r="M9" t="n">
-        <v>2.390233741195072</v>
+        <v>2.388745699627505</v>
       </c>
       <c r="N9" t="n">
-        <v>9.862241174073457</v>
+        <v>9.841970660766931</v>
       </c>
       <c r="O9" t="n">
-        <v>3.140420540958401</v>
+        <v>3.137191524399958</v>
       </c>
       <c r="P9" t="n">
-        <v>363.4963463644353</v>
+        <v>363.5095286213034</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34520,28 +34618,28 @@
         <v>0.097</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09134148842343107</v>
+        <v>-0.09234649711173702</v>
       </c>
       <c r="J10" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="K10" t="n">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04068678412390325</v>
+        <v>0.04176186305807394</v>
       </c>
       <c r="M10" t="n">
-        <v>2.277928703878335</v>
+        <v>2.275781241950492</v>
       </c>
       <c r="N10" t="n">
-        <v>8.89360296907663</v>
+        <v>8.87449473734276</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9822144404916</v>
+        <v>2.979009019345655</v>
       </c>
       <c r="P10" t="n">
-        <v>373.4203750867156</v>
+        <v>373.4324298382842</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34579,7 +34677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K667"/>
+  <dimension ref="A1:K669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72589,6 +72687,120 @@
         </is>
       </c>
     </row>
+    <row r="668">
+      <c r="A668" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-22 22:20:39+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>-45.260320104305244,170.86119886112988</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>-45.260853822899435,170.86070039924118</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>-45.26127541219719,170.86004259333006</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>-45.26174140328099,170.8594653075647</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>-45.26231544305003,170.85909847383832</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>-45.26293231705511,170.8589069173326</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>-45.26353826956223,170.85871710138932</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>-45.264141316869235,170.85869638637462</t>
+        </is>
+      </c>
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>-45.26474567627241,170.85889608547453</t>
+        </is>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:48+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>-45.26033001859534,170.86121416649448</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>-45.260852138164424,170.86069828837307</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>-45.26127295658643,170.86003922395466</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>-45.26173777424008,170.85945725055674</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>-45.26231248950533,170.85908876026065</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>-45.26293001395872,170.85889685694235</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>-45.263536647477316,170.8587061261763</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>-45.26414117803997,170.8586869592173</t>
+        </is>
+      </c>
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>-45.264745926416325,170.85889112861483</t>
+        </is>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0481/nzd0481.xlsx
+++ b/data/nzd0481/nzd0481.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K669"/>
+  <dimension ref="A1:K673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26529,6 +26529,162 @@
         <v>369.24</v>
       </c>
       <c r="K669" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>334.94</v>
+      </c>
+      <c r="C670" t="n">
+        <v>343.84</v>
+      </c>
+      <c r="D670" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="E670" t="n">
+        <v>342.19</v>
+      </c>
+      <c r="F670" t="n">
+        <v>344.76</v>
+      </c>
+      <c r="G670" t="n">
+        <v>350.77</v>
+      </c>
+      <c r="H670" t="n">
+        <v>354.98</v>
+      </c>
+      <c r="I670" t="n">
+        <v>361.68</v>
+      </c>
+      <c r="J670" t="n">
+        <v>369.57</v>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>336.24</v>
+      </c>
+      <c r="C671" t="n">
+        <v>344.34</v>
+      </c>
+      <c r="D671" t="n">
+        <v>350.52</v>
+      </c>
+      <c r="E671" t="n">
+        <v>342.61</v>
+      </c>
+      <c r="F671" t="n">
+        <v>346.02</v>
+      </c>
+      <c r="G671" t="n">
+        <v>350.94</v>
+      </c>
+      <c r="H671" t="n">
+        <v>356.17</v>
+      </c>
+      <c r="I671" t="n">
+        <v>361.88</v>
+      </c>
+      <c r="J671" t="n">
+        <v>368.59</v>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>336.71</v>
+      </c>
+      <c r="C672" t="n">
+        <v>344.69</v>
+      </c>
+      <c r="D672" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="E672" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="F672" t="n">
+        <v>345.57</v>
+      </c>
+      <c r="G672" t="n">
+        <v>350.1</v>
+      </c>
+      <c r="H672" t="n">
+        <v>355.21</v>
+      </c>
+      <c r="I672" t="n">
+        <v>361.1</v>
+      </c>
+      <c r="J672" t="n">
+        <v>366.68</v>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>336.31</v>
+      </c>
+      <c r="C673" t="n">
+        <v>344.3</v>
+      </c>
+      <c r="D673" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="E673" t="n">
+        <v>342.26</v>
+      </c>
+      <c r="F673" t="n">
+        <v>345.52</v>
+      </c>
+      <c r="G673" t="n">
+        <v>350.23</v>
+      </c>
+      <c r="H673" t="n">
+        <v>354.87</v>
+      </c>
+      <c r="I673" t="n">
+        <v>360.26</v>
+      </c>
+      <c r="J673" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="K673" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26545,7 +26701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B727"/>
+  <dimension ref="A1:B731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33818,6 +33974,46 @@
       </c>
       <c r="B727" t="n">
         <v>0.48</v>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B728" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B729" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B730" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B731" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -33986,28 +34182,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.08196957488010517</v>
+        <v>-0.07754418706754374</v>
       </c>
       <c r="J2" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K2" t="n">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004043084223136373</v>
+        <v>0.003662236814327868</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4093745514876</v>
+        <v>7.386112907579849</v>
       </c>
       <c r="N2" t="n">
-        <v>74.48512860553161</v>
+        <v>74.1133421298057</v>
       </c>
       <c r="O2" t="n">
-        <v>8.630476731069473</v>
+        <v>8.608910623871392</v>
       </c>
       <c r="P2" t="n">
-        <v>334.7741353917766</v>
+        <v>334.7204115334112</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34068,28 +34264,28 @@
         <v>0.073</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1716124706758435</v>
+        <v>-0.1730734946572715</v>
       </c>
       <c r="J3" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K3" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1021818873325893</v>
+        <v>0.1048596391838033</v>
       </c>
       <c r="M3" t="n">
-        <v>2.807054315148046</v>
+        <v>2.797354728763911</v>
       </c>
       <c r="N3" t="n">
-        <v>11.73603314144617</v>
+        <v>11.67442816645136</v>
       </c>
       <c r="O3" t="n">
-        <v>3.425789418724707</v>
+        <v>3.416786233648713</v>
       </c>
       <c r="P3" t="n">
-        <v>349.9929399941998</v>
+        <v>350.0105992478949</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34150,28 +34346,28 @@
         <v>0.0871</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06731190291529399</v>
+        <v>-0.06887765472307951</v>
       </c>
       <c r="J4" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K4" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02315835169218272</v>
+        <v>0.02449259341451127</v>
       </c>
       <c r="M4" t="n">
-        <v>2.388398089963014</v>
+        <v>2.380747795887269</v>
       </c>
       <c r="N4" t="n">
-        <v>8.667811463311553</v>
+        <v>8.626690379648627</v>
       </c>
       <c r="O4" t="n">
-        <v>2.944114716398047</v>
+        <v>2.937122806361462</v>
       </c>
       <c r="P4" t="n">
-        <v>352.8693017249809</v>
+        <v>352.8882364422486</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34228,28 +34424,28 @@
         <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1272526992709782</v>
+        <v>-0.1298945206021577</v>
       </c>
       <c r="J5" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K5" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0750860581173064</v>
+        <v>0.07869776119269745</v>
       </c>
       <c r="M5" t="n">
-        <v>2.291707319639645</v>
+        <v>2.289477526146452</v>
       </c>
       <c r="N5" t="n">
-        <v>9.046596584727142</v>
+        <v>9.018060046611788</v>
       </c>
       <c r="O5" t="n">
-        <v>3.007756071347399</v>
+        <v>3.003008499257334</v>
       </c>
       <c r="P5" t="n">
-        <v>347.8495013851625</v>
+        <v>347.8814380687138</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34306,28 +34502,28 @@
         <v>0.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1711516671633847</v>
+        <v>-0.1717724128183867</v>
       </c>
       <c r="J6" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K6" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1607423552901694</v>
+        <v>0.1633859488062056</v>
       </c>
       <c r="M6" t="n">
-        <v>2.012333496273082</v>
+        <v>2.003277441444837</v>
       </c>
       <c r="N6" t="n">
-        <v>6.936436949889417</v>
+        <v>6.897774509994584</v>
       </c>
       <c r="O6" t="n">
-        <v>2.633711629979527</v>
+        <v>2.6263614583668</v>
       </c>
       <c r="P6" t="n">
-        <v>350.4951891614884</v>
+        <v>350.5026899780518</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34384,28 +34580,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1922245426062458</v>
+        <v>-0.1970601791553456</v>
       </c>
       <c r="J7" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K7" t="n">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1460055049711214</v>
+        <v>0.1528239571906354</v>
       </c>
       <c r="M7" t="n">
-        <v>2.464654951342004</v>
+        <v>2.472129881774132</v>
       </c>
       <c r="N7" t="n">
-        <v>9.763797059530846</v>
+        <v>9.789983837095045</v>
       </c>
       <c r="O7" t="n">
-        <v>3.124707515837418</v>
+        <v>3.128894986587924</v>
       </c>
       <c r="P7" t="n">
-        <v>359.3930251422227</v>
+        <v>359.4516235428907</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34462,28 +34658,28 @@
         <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.185971414677683</v>
+        <v>-0.1895062523276232</v>
       </c>
       <c r="J8" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K8" t="n">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1659356758314552</v>
+        <v>0.1721686349874381</v>
       </c>
       <c r="M8" t="n">
-        <v>2.129113622760431</v>
+        <v>2.134388631461338</v>
       </c>
       <c r="N8" t="n">
-        <v>7.853575035354067</v>
+        <v>7.853024100575476</v>
       </c>
       <c r="O8" t="n">
-        <v>2.802423065019639</v>
+        <v>2.802324767148782</v>
       </c>
       <c r="P8" t="n">
-        <v>363.0066467430654</v>
+        <v>363.0494808552009</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34540,28 +34736,28 @@
         <v>0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07311423093058911</v>
+        <v>-0.0735484673804495</v>
       </c>
       <c r="J9" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K9" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02404154069607967</v>
+        <v>0.02461454709819311</v>
       </c>
       <c r="M9" t="n">
-        <v>2.388745699627505</v>
+        <v>2.377997587158423</v>
       </c>
       <c r="N9" t="n">
-        <v>9.841970660766931</v>
+        <v>9.786409636094513</v>
       </c>
       <c r="O9" t="n">
-        <v>3.137191524399958</v>
+        <v>3.128323774179155</v>
       </c>
       <c r="P9" t="n">
-        <v>363.5095286213034</v>
+        <v>363.5147863068993</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34618,28 +34814,28 @@
         <v>0.097</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09234649711173702</v>
+        <v>-0.09648764512429871</v>
       </c>
       <c r="J10" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="K10" t="n">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04176186305807394</v>
+        <v>0.04560595058366923</v>
       </c>
       <c r="M10" t="n">
-        <v>2.275781241950492</v>
+        <v>2.28099232913646</v>
       </c>
       <c r="N10" t="n">
-        <v>8.87449473734276</v>
+        <v>8.894905446067883</v>
       </c>
       <c r="O10" t="n">
-        <v>2.979009019345655</v>
+        <v>2.982432806630836</v>
       </c>
       <c r="P10" t="n">
-        <v>373.4324298382842</v>
+        <v>373.4825129967141</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34677,7 +34873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K669"/>
+  <dimension ref="A1:K673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72801,6 +72997,234 @@
         </is>
       </c>
     </row>
+    <row r="670">
+      <c r="A670" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>-45.26034832657372,170.8612424297892</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>-45.26087639834498,170.86072868488577</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>-45.261292019878006,170.86006538095558</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>-45.26174440328772,170.85947196802545</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>-45.262315834483616,170.85909976118003</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>-45.26293101289221,170.85890122048502</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>-45.26353701613308,170.8587086205428</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>-45.26414158702126,170.85871473111337</t>
+        </is>
+      </c>
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>-45.264745714756096,170.85889532288073</t>
+        </is>
+      </c>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>-45.26035623367193,170.86125463653343</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>-45.2608797678139,170.86073290662569</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>-45.261294669351976,170.86006901633672</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>-45.261746435550144,170.8594764799508</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>-45.26232031817627,170.85911450709528</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>-45.262931484610746,170.85890328104688</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>-45.263539209633684,170.85872346202447</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>-45.26414162454215,170.85871727899377</t>
+        </is>
+      </c>
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>-45.264746343322386,170.85888286718193</t>
+        </is>
+      </c>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>-45.260359092391745,170.86125904974176</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>-45.260882126442056,170.86073586184392</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>-45.26128937040393,170.86006174557474</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>-45.26174614522695,170.85947583539004</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>-45.26231871685768,170.8591092406967</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>-45.26292915376588,170.8588930994474</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>-45.26353744008712,170.85871148906438</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>-45.264141478210384,170.85870734226023</t>
+        </is>
+      </c>
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>-45.264747568381324,170.85885859127856</t>
+        </is>
+      </c>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>-45.26035665943873,170.86125529381974</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>-45.26087949825639,170.86073256888648</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>-45.261285428503264,170.86005633683803</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>-45.26174474199813,170.85947272001295</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>-45.26231853893337,170.85910865554132</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>-45.26292951449193,170.8588946751711</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>-45.263536813372404,170.85870724864122</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>-45.26414132062136,170.85869664116265</t>
+        </is>
+      </c>
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>-45.26474794038773,170.85885121953808</t>
+        </is>
+      </c>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0481/nzd0481.xlsx
+++ b/data/nzd0481/nzd0481.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K673"/>
+  <dimension ref="A1:K674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26685,6 +26685,45 @@
         <v>366.1</v>
       </c>
       <c r="K673" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>337.12</v>
+      </c>
+      <c r="C674" t="n">
+        <v>343.83</v>
+      </c>
+      <c r="D674" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="E674" t="n">
+        <v>341.34</v>
+      </c>
+      <c r="F674" t="n">
+        <v>343.86</v>
+      </c>
+      <c r="G674" t="n">
+        <v>348.86</v>
+      </c>
+      <c r="H674" t="n">
+        <v>353.02</v>
+      </c>
+      <c r="I674" t="n">
+        <v>358.8</v>
+      </c>
+      <c r="J674" t="n">
+        <v>364.26</v>
+      </c>
+      <c r="K674" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26701,7 +26740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B731"/>
+  <dimension ref="A1:B732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34014,6 +34053,16 @@
       </c>
       <c r="B731" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>-0.06</v>
       </c>
     </row>
   </sheetData>
@@ -34182,28 +34231,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07754418706754374</v>
+        <v>-0.07610550892345118</v>
       </c>
       <c r="J2" t="n">
+        <v>673</v>
+      </c>
+      <c r="K2" t="n">
         <v>672</v>
       </c>
-      <c r="K2" t="n">
-        <v>671</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.003662236814327868</v>
+        <v>0.00353787698752106</v>
       </c>
       <c r="M2" t="n">
-        <v>7.386112907579849</v>
+        <v>7.381907131547339</v>
       </c>
       <c r="N2" t="n">
-        <v>74.1133421298057</v>
+        <v>74.03253761613244</v>
       </c>
       <c r="O2" t="n">
-        <v>8.608910623871392</v>
+        <v>8.604216269721052</v>
       </c>
       <c r="P2" t="n">
-        <v>334.7204115334112</v>
+        <v>334.7028808699967</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34264,28 +34313,28 @@
         <v>0.073</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1730734946572715</v>
+        <v>-0.1735767144528708</v>
       </c>
       <c r="J3" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K3" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1048596391838033</v>
+        <v>0.1056754049788642</v>
       </c>
       <c r="M3" t="n">
-        <v>2.797354728763911</v>
+        <v>2.795584303826588</v>
       </c>
       <c r="N3" t="n">
-        <v>11.67442816645136</v>
+        <v>11.66073147617616</v>
       </c>
       <c r="O3" t="n">
-        <v>3.416786233648713</v>
+        <v>3.414781321867648</v>
       </c>
       <c r="P3" t="n">
-        <v>350.0105992478949</v>
+        <v>350.0167064961409</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34346,28 +34395,28 @@
         <v>0.0871</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06887765472307951</v>
+        <v>-0.07016305060740745</v>
       </c>
       <c r="J4" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K4" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02449259341451127</v>
+        <v>0.02540192148916776</v>
       </c>
       <c r="M4" t="n">
-        <v>2.380747795887269</v>
+        <v>2.382558008775137</v>
       </c>
       <c r="N4" t="n">
-        <v>8.626690379648627</v>
+        <v>8.637688177358189</v>
       </c>
       <c r="O4" t="n">
-        <v>2.937122806361462</v>
+        <v>2.938994416013442</v>
       </c>
       <c r="P4" t="n">
-        <v>352.8882364422486</v>
+        <v>352.9038364481081</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34424,28 +34473,28 @@
         <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1298945206021577</v>
+        <v>-0.1308816984935625</v>
       </c>
       <c r="J5" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K5" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07869776119269745</v>
+        <v>0.07992089370502919</v>
       </c>
       <c r="M5" t="n">
-        <v>2.289477526146452</v>
+        <v>2.290318223832208</v>
       </c>
       <c r="N5" t="n">
-        <v>9.018060046611788</v>
+        <v>9.018707363255075</v>
       </c>
       <c r="O5" t="n">
-        <v>3.003008499257334</v>
+        <v>3.003116275347173</v>
       </c>
       <c r="P5" t="n">
-        <v>347.8814380687138</v>
+        <v>347.8934187986025</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34502,28 +34551,28 @@
         <v>0.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1717724128183867</v>
+        <v>-0.1724335845531574</v>
       </c>
       <c r="J6" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K6" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1633859488062056</v>
+        <v>0.1647487460326879</v>
       </c>
       <c r="M6" t="n">
-        <v>2.003277441444837</v>
+        <v>2.003190043495732</v>
       </c>
       <c r="N6" t="n">
-        <v>6.897774509994584</v>
+        <v>6.893826436769026</v>
       </c>
       <c r="O6" t="n">
-        <v>2.6263614583668</v>
+        <v>2.625609726667127</v>
       </c>
       <c r="P6" t="n">
-        <v>350.5026899780518</v>
+        <v>350.5107141852725</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34580,28 +34629,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1970601791553456</v>
+        <v>-0.1987784658416177</v>
       </c>
       <c r="J7" t="n">
+        <v>673</v>
+      </c>
+      <c r="K7" t="n">
         <v>672</v>
       </c>
-      <c r="K7" t="n">
-        <v>671</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.1528239571906354</v>
+        <v>0.1549351517215365</v>
       </c>
       <c r="M7" t="n">
-        <v>2.472129881774132</v>
+        <v>2.476306771701809</v>
       </c>
       <c r="N7" t="n">
-        <v>9.789983837095045</v>
+        <v>9.817745163899705</v>
       </c>
       <c r="O7" t="n">
-        <v>3.128894986587924</v>
+        <v>3.133328128986765</v>
       </c>
       <c r="P7" t="n">
-        <v>359.4516235428907</v>
+        <v>359.4725255986152</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34658,28 +34707,28 @@
         <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1895062523276232</v>
+        <v>-0.1911087155707761</v>
       </c>
       <c r="J8" t="n">
+        <v>673</v>
+      </c>
+      <c r="K8" t="n">
         <v>672</v>
       </c>
-      <c r="K8" t="n">
-        <v>671</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.1721686349874381</v>
+        <v>0.1743644491141557</v>
       </c>
       <c r="M8" t="n">
-        <v>2.134388631461338</v>
+        <v>2.139342376126919</v>
       </c>
       <c r="N8" t="n">
-        <v>7.853024100575476</v>
+        <v>7.878153549084733</v>
       </c>
       <c r="O8" t="n">
-        <v>2.802324767148782</v>
+        <v>2.806804864803525</v>
       </c>
       <c r="P8" t="n">
-        <v>363.0494808552009</v>
+        <v>363.0689739795279</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34736,28 +34785,28 @@
         <v>0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0735484673804495</v>
+        <v>-0.07443036616777249</v>
       </c>
       <c r="J9" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K9" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02461454709819311</v>
+        <v>0.02524309997674357</v>
       </c>
       <c r="M9" t="n">
-        <v>2.377997587158423</v>
+        <v>2.378941814807218</v>
       </c>
       <c r="N9" t="n">
-        <v>9.786409636094513</v>
+        <v>9.783078887855316</v>
       </c>
       <c r="O9" t="n">
-        <v>3.128323774179155</v>
+        <v>3.127791375372615</v>
       </c>
       <c r="P9" t="n">
-        <v>363.5147863068993</v>
+        <v>363.5254893334279</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34814,28 +34863,28 @@
         <v>0.097</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09648764512429871</v>
+        <v>-0.09861921183853206</v>
       </c>
       <c r="J10" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K10" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04560595058366923</v>
+        <v>0.04735745899802335</v>
       </c>
       <c r="M10" t="n">
-        <v>2.28099232913646</v>
+        <v>2.287288471044806</v>
       </c>
       <c r="N10" t="n">
-        <v>8.894905446067883</v>
+        <v>8.947181508322922</v>
       </c>
       <c r="O10" t="n">
-        <v>2.982432806630836</v>
+        <v>2.991183964306261</v>
       </c>
       <c r="P10" t="n">
-        <v>373.4825129967141</v>
+        <v>373.5083824223419</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34873,7 +34922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K673"/>
+  <dimension ref="A1:K674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73225,6 +73274,63 @@
         </is>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:14:23+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-45.26036158616848,170.8612628995622</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-45.2608763309556,170.86072860045098</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-45.26127218113039,170.8600381599414</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>-45.26174029037518,170.8594628367488</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>-45.26231263184486,170.85908922838487</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-45.26292571299325,170.8588780694688</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>-45.26353340330438,170.85868417575216</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>-45.26414104671427,170.85867804163613</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>-45.26474912054281,170.85882783332644</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0481/nzd0481.xlsx
+++ b/data/nzd0481/nzd0481.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K674"/>
+  <dimension ref="A1:K680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26724,6 +26724,240 @@
         <v>364.26</v>
       </c>
       <c r="K674" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>336.54</v>
+      </c>
+      <c r="C675" t="n">
+        <v>343.63</v>
+      </c>
+      <c r="D675" t="n">
+        <v>347.04</v>
+      </c>
+      <c r="E675" t="n">
+        <v>341.64</v>
+      </c>
+      <c r="F675" t="n">
+        <v>343.93</v>
+      </c>
+      <c r="G675" t="n">
+        <v>349.19</v>
+      </c>
+      <c r="H675" t="n">
+        <v>353.22</v>
+      </c>
+      <c r="I675" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="J675" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>334.72</v>
+      </c>
+      <c r="C676" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="D676" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="E676" t="n">
+        <v>340.36</v>
+      </c>
+      <c r="F676" t="n">
+        <v>342.3</v>
+      </c>
+      <c r="G676" t="n">
+        <v>350.15</v>
+      </c>
+      <c r="H676" t="n">
+        <v>353.31</v>
+      </c>
+      <c r="I676" t="n">
+        <v>358.23</v>
+      </c>
+      <c r="J676" t="n">
+        <v>363.96</v>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>334.05</v>
+      </c>
+      <c r="C677" t="n">
+        <v>343.2</v>
+      </c>
+      <c r="D677" t="n">
+        <v>346.55</v>
+      </c>
+      <c r="E677" t="n">
+        <v>340.52</v>
+      </c>
+      <c r="F677" t="n">
+        <v>342.57</v>
+      </c>
+      <c r="G677" t="n">
+        <v>351.01</v>
+      </c>
+      <c r="H677" t="n">
+        <v>354.18</v>
+      </c>
+      <c r="I677" t="n">
+        <v>358.7</v>
+      </c>
+      <c r="J677" t="n">
+        <v>365.38</v>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>333.32</v>
+      </c>
+      <c r="C678" t="n">
+        <v>342.99</v>
+      </c>
+      <c r="D678" t="n">
+        <v>346.57</v>
+      </c>
+      <c r="E678" t="n">
+        <v>341.04</v>
+      </c>
+      <c r="F678" t="n">
+        <v>342.59</v>
+      </c>
+      <c r="G678" t="n">
+        <v>351.05</v>
+      </c>
+      <c r="H678" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="I678" t="n">
+        <v>359</v>
+      </c>
+      <c r="J678" t="n">
+        <v>365.52</v>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>333.42</v>
+      </c>
+      <c r="C679" t="n">
+        <v>343.74</v>
+      </c>
+      <c r="D679" t="n">
+        <v>347.38</v>
+      </c>
+      <c r="E679" t="n">
+        <v>341.44</v>
+      </c>
+      <c r="F679" t="n">
+        <v>343.53</v>
+      </c>
+      <c r="G679" t="n">
+        <v>352.27</v>
+      </c>
+      <c r="H679" t="n">
+        <v>356.53</v>
+      </c>
+      <c r="I679" t="n">
+        <v>359.68</v>
+      </c>
+      <c r="J679" t="n">
+        <v>367.43</v>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>333.11</v>
+      </c>
+      <c r="C680" t="n">
+        <v>344.26</v>
+      </c>
+      <c r="D680" t="n">
+        <v>348.05</v>
+      </c>
+      <c r="E680" t="n">
+        <v>342.17</v>
+      </c>
+      <c r="F680" t="n">
+        <v>343.76</v>
+      </c>
+      <c r="G680" t="n">
+        <v>353.01</v>
+      </c>
+      <c r="H680" t="n">
+        <v>357.72</v>
+      </c>
+      <c r="I680" t="n">
+        <v>360.06</v>
+      </c>
+      <c r="J680" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="K680" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26740,7 +26974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B732"/>
+  <dimension ref="A1:B738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34063,6 +34297,66 @@
       </c>
       <c r="B732" t="n">
         <v>-0.06</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>-0.84</v>
       </c>
     </row>
   </sheetData>
@@ -34231,28 +34525,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07610550892345118</v>
+        <v>-0.07323115672412674</v>
       </c>
       <c r="J2" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="K2" t="n">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00353787698752106</v>
+        <v>0.003337392349397006</v>
       </c>
       <c r="M2" t="n">
-        <v>7.381907131547339</v>
+        <v>7.329987790982341</v>
       </c>
       <c r="N2" t="n">
-        <v>74.03253761613244</v>
+        <v>73.40953397596692</v>
       </c>
       <c r="O2" t="n">
-        <v>8.604216269721052</v>
+        <v>8.567936389584538</v>
       </c>
       <c r="P2" t="n">
-        <v>334.7028808699967</v>
+        <v>334.6678017151727</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34313,28 +34607,28 @@
         <v>0.073</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1735767144528708</v>
+        <v>-0.1771260075516217</v>
       </c>
       <c r="J3" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="K3" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1056754049788642</v>
+        <v>0.1111365618067041</v>
       </c>
       <c r="M3" t="n">
-        <v>2.795584303826588</v>
+        <v>2.787470035931777</v>
       </c>
       <c r="N3" t="n">
-        <v>11.66073147617616</v>
+        <v>11.59001095810178</v>
       </c>
       <c r="O3" t="n">
-        <v>3.414781321867648</v>
+        <v>3.40441051550805</v>
       </c>
       <c r="P3" t="n">
-        <v>350.0167064961409</v>
+        <v>350.0598727376039</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34395,28 +34689,28 @@
         <v>0.0871</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07016305060740745</v>
+        <v>-0.07774319409187121</v>
       </c>
       <c r="J4" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="K4" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02540192148916776</v>
+        <v>0.03107659770865256</v>
       </c>
       <c r="M4" t="n">
-        <v>2.382558008775137</v>
+        <v>2.393289001074491</v>
       </c>
       <c r="N4" t="n">
-        <v>8.637688177358189</v>
+        <v>8.704059131214905</v>
       </c>
       <c r="O4" t="n">
-        <v>2.938994416013442</v>
+        <v>2.950264247692892</v>
       </c>
       <c r="P4" t="n">
-        <v>352.9038364481081</v>
+        <v>352.9960275757098</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34473,28 +34767,28 @@
         <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1308816984935625</v>
+        <v>-0.1369071148068284</v>
       </c>
       <c r="J5" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="K5" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07992089370502919</v>
+        <v>0.08747985886010201</v>
       </c>
       <c r="M5" t="n">
-        <v>2.290318223832208</v>
+        <v>2.295875062303303</v>
       </c>
       <c r="N5" t="n">
-        <v>9.018707363255075</v>
+        <v>9.030826845520151</v>
       </c>
       <c r="O5" t="n">
-        <v>3.003116275347173</v>
+        <v>3.005133415594082</v>
       </c>
       <c r="P5" t="n">
-        <v>347.8934187986025</v>
+        <v>347.9667010210061</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34551,28 +34845,28 @@
         <v>0.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1724335845531574</v>
+        <v>-0.1776890552561886</v>
       </c>
       <c r="J6" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="K6" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1647487460326879</v>
+        <v>0.1744001664881716</v>
       </c>
       <c r="M6" t="n">
-        <v>2.003190043495732</v>
+        <v>2.0084478714478</v>
       </c>
       <c r="N6" t="n">
-        <v>6.893826436769026</v>
+        <v>6.90375151813934</v>
       </c>
       <c r="O6" t="n">
-        <v>2.625609726667127</v>
+        <v>2.627499099550624</v>
       </c>
       <c r="P6" t="n">
-        <v>350.5107141852725</v>
+        <v>350.5746349368967</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34629,28 +34923,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1987784658416177</v>
+        <v>-0.2045328911577335</v>
       </c>
       <c r="J7" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="K7" t="n">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1549351517215365</v>
+        <v>0.1638106072991048</v>
       </c>
       <c r="M7" t="n">
-        <v>2.476306771701809</v>
+        <v>2.4804601357642</v>
       </c>
       <c r="N7" t="n">
-        <v>9.817745163899705</v>
+        <v>9.825347801737442</v>
       </c>
       <c r="O7" t="n">
-        <v>3.133328128986765</v>
+        <v>3.134541083115268</v>
       </c>
       <c r="P7" t="n">
-        <v>359.4725255986152</v>
+        <v>359.5426536377067</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34707,28 +35001,28 @@
         <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1911087155707761</v>
+        <v>-0.1966544838900573</v>
       </c>
       <c r="J8" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="K8" t="n">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1743644491141557</v>
+        <v>0.1836907141800558</v>
       </c>
       <c r="M8" t="n">
-        <v>2.139342376126919</v>
+        <v>2.14877936805417</v>
       </c>
       <c r="N8" t="n">
-        <v>7.878153549084733</v>
+        <v>7.907409400914347</v>
       </c>
       <c r="O8" t="n">
-        <v>2.806804864803525</v>
+        <v>2.812011628872531</v>
       </c>
       <c r="P8" t="n">
-        <v>363.0689739795279</v>
+        <v>363.1365501494821</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34785,28 +35079,28 @@
         <v>0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07443036616777249</v>
+        <v>-0.07906988477652069</v>
       </c>
       <c r="J9" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="K9" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02524309997674357</v>
+        <v>0.02875931650433705</v>
       </c>
       <c r="M9" t="n">
-        <v>2.378941814807218</v>
+        <v>2.381506889079288</v>
       </c>
       <c r="N9" t="n">
-        <v>9.783078887855316</v>
+        <v>9.752402363148606</v>
       </c>
       <c r="O9" t="n">
-        <v>3.127791375372615</v>
+        <v>3.122883661481581</v>
       </c>
       <c r="P9" t="n">
-        <v>363.5254893334279</v>
+        <v>363.5819094754898</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34863,28 +35157,28 @@
         <v>0.097</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.09861921183853206</v>
+        <v>-0.1082400423418228</v>
       </c>
       <c r="J10" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="K10" t="n">
-        <v>673</v>
+        <v>679</v>
       </c>
       <c r="L10" t="n">
-        <v>0.04735745899802335</v>
+        <v>0.05603504166142381</v>
       </c>
       <c r="M10" t="n">
-        <v>2.287288471044806</v>
+        <v>2.310452879368129</v>
       </c>
       <c r="N10" t="n">
-        <v>8.947181508322922</v>
+        <v>9.116185928868877</v>
       </c>
       <c r="O10" t="n">
-        <v>2.991183964306261</v>
+        <v>3.019302225493314</v>
       </c>
       <c r="P10" t="n">
-        <v>373.5083824223419</v>
+        <v>373.6253705939482</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34922,7 +35216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K674"/>
+  <dimension ref="A1:K680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73331,6 +73625,348 @@
         </is>
       </c>
     </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:13:44+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-45.26035805838672,170.86125745347485</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-45.260874983168,170.86072691175517</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-45.26127218113039,170.8600381599414</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-45.26174174199145,170.85946605955218</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-45.262312880939014,170.85909004760222</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-45.26292662868292,170.85888206938228</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>-45.263533771960596,170.8586866701184</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>-45.26414103733385,170.85867740466603</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>-45.26474928088958,170.858824655852</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:53+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>-45.26034698844928,170.86124036403282</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>-45.26087174847763,170.8607228588855</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-45.261268045364616,170.8600324852047</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-45.26173554842804,170.8594523089257</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>-45.26230708060208,170.8590709715428</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>-45.262929292506655,170.85889370549498</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>-45.26353393785589,170.85868779258323</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>-45.26414093977713,170.85867078017722</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>-45.264749312958934,170.8588240203571</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>-45.26034291325191,170.86123407286627</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>-45.26087208542456,170.8607232810594</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>-45.26126901468474,170.86003381522104</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>-45.261736322623555,170.85945402775383</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>-45.262308041394306,170.8590741313806</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>-45.262931678847764,170.85890412951355</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>-45.263535541509754,170.85869864307682</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>-45.2641410279534,170.85867676769598</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>-45.26474840218811,170.85884206841192</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>-45.2603384731111,170.8612272183127</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>-45.26087067024749,170.86072150792907</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>-45.261269143927436,170.86003399255654</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>-45.26173883875881,170.85945961394563</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>-45.262308112564085,170.85907436544264</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>-45.26293178984036,170.85890461435164</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>-45.263537403221555,170.85871123962772</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>-45.26414108423598,170.85868058951644</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>-45.26474831239365,170.85884384779754</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>-45.2603390813496,170.86122815729257</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>-45.26087572445118,170.86072784053786</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>-45.26127437825583,170.86004117464563</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>-45.26174077424727,170.85946391101658</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>-45.26231145754373,170.85908536636026</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>-45.262935175113284,170.85891940191448</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>-45.26353987321333,170.85872795188467</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>-45.264141211809324,170.8586892523096</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>-45.26474708733785,170.85886812370146</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>-45.26033719581026,170.861225246455</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>-45.26087922869887,170.86073223114727</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>-45.26127870788516,170.86004711538698</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>-45.26174430651333,170.85947175317185</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>-45.26231227599604,170.85908805807438</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>-45.262937228474634,170.8589283714207</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>-45.26354206671145,170.85874279336792</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>-45.26414128310004,170.85869409328228</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>-45.264746574223956,170.85887829161905</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0481/nzd0481.xlsx
+++ b/data/nzd0481/nzd0481.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K680"/>
+  <dimension ref="A1:K684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26958,6 +26958,162 @@
         <v>368.23</v>
       </c>
       <c r="K680" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="C681" t="n">
+        <v>342.58</v>
+      </c>
+      <c r="D681" t="n">
+        <v>346.03</v>
+      </c>
+      <c r="E681" t="n">
+        <v>341.04</v>
+      </c>
+      <c r="F681" t="n">
+        <v>341.63</v>
+      </c>
+      <c r="G681" t="n">
+        <v>352</v>
+      </c>
+      <c r="H681" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="I681" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="J681" t="n">
+        <v>366.87</v>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>329.37</v>
+      </c>
+      <c r="C682" t="n">
+        <v>342.37</v>
+      </c>
+      <c r="D682" t="n">
+        <v>346.16</v>
+      </c>
+      <c r="E682" t="n">
+        <v>341.15</v>
+      </c>
+      <c r="F682" t="n">
+        <v>342.18</v>
+      </c>
+      <c r="G682" t="n">
+        <v>352.24</v>
+      </c>
+      <c r="H682" t="n">
+        <v>356.28</v>
+      </c>
+      <c r="I682" t="n">
+        <v>358.61</v>
+      </c>
+      <c r="J682" t="n">
+        <v>367.11</v>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:35+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>328.69</v>
+      </c>
+      <c r="C683" t="n">
+        <v>341.44</v>
+      </c>
+      <c r="D683" t="n">
+        <v>344.64</v>
+      </c>
+      <c r="E683" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="F683" t="n">
+        <v>343.1</v>
+      </c>
+      <c r="G683" t="n">
+        <v>351.38</v>
+      </c>
+      <c r="H683" t="n">
+        <v>355.29</v>
+      </c>
+      <c r="I683" t="n">
+        <v>357.67</v>
+      </c>
+      <c r="J683" t="n">
+        <v>367.11</v>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>324.68</v>
+      </c>
+      <c r="C684" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="D684" t="n">
+        <v>343.76</v>
+      </c>
+      <c r="E684" t="n">
+        <v>337.19</v>
+      </c>
+      <c r="F684" t="n">
+        <v>342.59</v>
+      </c>
+      <c r="G684" t="n">
+        <v>351.02</v>
+      </c>
+      <c r="H684" t="n">
+        <v>355.16</v>
+      </c>
+      <c r="I684" t="n">
+        <v>357.49</v>
+      </c>
+      <c r="J684" t="n">
+        <v>367.22</v>
+      </c>
+      <c r="K684" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26974,7 +27130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B738"/>
+  <dimension ref="A1:B743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34357,6 +34513,56 @@
       </c>
       <c r="B738" t="n">
         <v>-0.84</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>
@@ -34525,28 +34731,28 @@
         <v>0.08989999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07323115672412674</v>
+        <v>-0.07864231467048605</v>
       </c>
       <c r="J2" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="K2" t="n">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003337392349397006</v>
+        <v>0.003887691820816386</v>
       </c>
       <c r="M2" t="n">
-        <v>7.329987790982341</v>
+        <v>7.31198056667101</v>
       </c>
       <c r="N2" t="n">
-        <v>73.40953397596692</v>
+        <v>73.11670598729704</v>
       </c>
       <c r="O2" t="n">
-        <v>8.567936389584538</v>
+        <v>8.550830719134664</v>
       </c>
       <c r="P2" t="n">
-        <v>334.6678017151727</v>
+        <v>334.7341645467084</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -34607,28 +34813,28 @@
         <v>0.073</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1771260075516217</v>
+        <v>-0.1821853018372498</v>
       </c>
       <c r="J3" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="K3" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1111365618067041</v>
+        <v>0.1171284524867879</v>
       </c>
       <c r="M3" t="n">
-        <v>2.787470035931777</v>
+        <v>2.79443742619259</v>
       </c>
       <c r="N3" t="n">
-        <v>11.59001095810178</v>
+        <v>11.63194594811062</v>
       </c>
       <c r="O3" t="n">
-        <v>3.40441051550805</v>
+        <v>3.41056387538932</v>
       </c>
       <c r="P3" t="n">
-        <v>350.0598727376039</v>
+        <v>350.1216710176288</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -34689,28 +34895,28 @@
         <v>0.0871</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07774319409187121</v>
+        <v>-0.08491540408417483</v>
       </c>
       <c r="J4" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="K4" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03107659770865256</v>
+        <v>0.03649841232032969</v>
       </c>
       <c r="M4" t="n">
-        <v>2.393289001074491</v>
+        <v>2.409603224939346</v>
       </c>
       <c r="N4" t="n">
-        <v>8.704059131214905</v>
+        <v>8.849974303120389</v>
       </c>
       <c r="O4" t="n">
-        <v>2.950264247692892</v>
+        <v>2.974890637169775</v>
       </c>
       <c r="P4" t="n">
-        <v>352.9960275757098</v>
+        <v>353.0836288178556</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34767,28 +34973,28 @@
         <v>0.0591</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1369071148068284</v>
+        <v>-0.1429186131121472</v>
       </c>
       <c r="J5" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="K5" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08747985886010201</v>
+        <v>0.09422653912120371</v>
       </c>
       <c r="M5" t="n">
-        <v>2.295875062303303</v>
+        <v>2.308714572738669</v>
       </c>
       <c r="N5" t="n">
-        <v>9.030826845520151</v>
+        <v>9.128817498706713</v>
       </c>
       <c r="O5" t="n">
-        <v>3.005133415594082</v>
+        <v>3.02139330420697</v>
       </c>
       <c r="P5" t="n">
-        <v>347.9667010210061</v>
+        <v>348.0401308585731</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34845,28 +35051,28 @@
         <v>0.0856</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1776890552561886</v>
+        <v>-0.1819627843854884</v>
       </c>
       <c r="J6" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="K6" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1744001664881716</v>
+        <v>0.1816988376714015</v>
       </c>
       <c r="M6" t="n">
-        <v>2.0084478714478</v>
+        <v>2.015773953295677</v>
       </c>
       <c r="N6" t="n">
-        <v>6.90375151813934</v>
+        <v>6.932929011614323</v>
       </c>
       <c r="O6" t="n">
-        <v>2.627499099550624</v>
+        <v>2.63304557720035</v>
       </c>
       <c r="P6" t="n">
-        <v>350.5746349368967</v>
+        <v>350.6268273526604</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34923,28 +35129,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2045328911577335</v>
+        <v>-0.207533333907773</v>
       </c>
       <c r="J7" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="K7" t="n">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1638106072991048</v>
+        <v>0.16908828660349</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4804601357642</v>
+        <v>2.479336832157166</v>
       </c>
       <c r="N7" t="n">
-        <v>9.825347801737442</v>
+        <v>9.802342020135077</v>
       </c>
       <c r="O7" t="n">
-        <v>3.134541083115268</v>
+        <v>3.130869211598446</v>
       </c>
       <c r="P7" t="n">
-        <v>359.5426536377067</v>
+        <v>359.5793857602725</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35001,28 +35207,28 @@
         <v>0.1419</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1966544838900573</v>
+        <v>-0.1992905483455285</v>
       </c>
       <c r="J8" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="K8" t="n">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1836907141800558</v>
+        <v>0.1890919235372172</v>
       </c>
       <c r="M8" t="n">
-        <v>2.14877936805417</v>
+        <v>2.149599578465834</v>
       </c>
       <c r="N8" t="n">
-        <v>7.907409400914347</v>
+        <v>7.888325423048846</v>
       </c>
       <c r="O8" t="n">
-        <v>2.812011628872531</v>
+        <v>2.808616282629018</v>
       </c>
       <c r="P8" t="n">
-        <v>363.1365501494821</v>
+        <v>363.1688222764834</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35079,28 +35285,28 @@
         <v>0.1237</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.07906988477652069</v>
+        <v>-0.08347747101036683</v>
       </c>
       <c r="J9" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="K9" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02875931650433705</v>
+        <v>0.03210188384580392</v>
       </c>
       <c r="M9" t="n">
-        <v>2.381506889079288</v>
+        <v>2.389813192416217</v>
       </c>
       <c r="N9" t="n">
-        <v>9.752402363148606</v>
+        <v>9.768508963586401</v>
       </c>
       <c r="O9" t="n">
-        <v>3.122883661481581</v>
+        <v>3.125461400111414</v>
       </c>
       <c r="P9" t="n">
-        <v>363.5819094754898</v>
+        <v>363.6357418776685</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35157,28 +35363,28 @@
         <v>0.097</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1082400423418228</v>
+        <v>-0.1127780216580961</v>
       </c>
       <c r="J10" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="K10" t="n">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="L10" t="n">
-        <v>0.05603504166142381</v>
+        <v>0.06077046864539748</v>
       </c>
       <c r="M10" t="n">
-        <v>2.310452879368129</v>
+        <v>2.317476355658108</v>
       </c>
       <c r="N10" t="n">
-        <v>9.116185928868877</v>
+        <v>9.139421028412245</v>
       </c>
       <c r="O10" t="n">
-        <v>3.019302225493314</v>
+        <v>3.023147536659805</v>
       </c>
       <c r="P10" t="n">
-        <v>373.6253705939482</v>
+        <v>373.6807927535064</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35216,7 +35422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K680"/>
+  <dimension ref="A1:K684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73967,6 +74173,234 @@
         </is>
       </c>
     </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:19:39+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>-45.26032314549873,170.86120355602642</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>-45.26086790728267,170.8607180461034</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>-45.26126565437492,170.86002920449792</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>-45.26173883875881,170.85945961394563</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>-45.2623046964136,170.8590631304643</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>-45.2629344259137,170.85891612925698</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>-45.26353941239415,170.8587248339262</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>-45.26414087974203,170.85866670356876</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>-45.26474744651706,170.85886100615903</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:17+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>-45.260314447684856,170.86119012862363</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>-45.26086649210552,170.86071627297332</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>-45.26126649445239,170.86003035717863</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>-45.26173937101815,170.8594607956401</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>-45.26230665358329,170.85906956717048</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>-45.2629350918689,170.85891903828588</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>-45.26353941239415,170.8587248339262</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>-45.26414101106862,170.8586756211498</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>-45.264747292583166,170.85886405653437</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:35+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>-45.260310311660945,170.8611837435664</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>-45.260860224892134,170.86070842054113</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-45.261256672007384,170.86001687968297</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-45.261726548403345,170.85943232755199</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>-45.2623099273936,170.85908033402544</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>-45.262932705529124,170.858908614266</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>-45.26353758754938,170.85871248681102</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>-45.26414083471561,170.85866364611238</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>-45.264747292583166,170.85886405653437</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-45.26028592127766,170.8611460905272</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-45.26084108630183,170.86068444108142</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-45.26125098532801,170.86000907692443</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-45.261720209674245,170.85941825465284</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-45.262308112564085,170.85907436544264</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>-45.26293170659593,170.85890425072307</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>-45.26353734792321,170.85871086547274</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>-45.26414080094575,170.8586613530201</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>-45.2647472220301,170.85886545462307</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
